--- a/Clean data/Customers.xlsx
+++ b/Clean data/Customers.xlsx
@@ -5,31 +5,43 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fjatakalula\Clean data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fjatakalula\impaza\Clean data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6936"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10848"/>
   </bookViews>
   <sheets>
-    <sheet name="NOVEMBER BILL DUE LIST" sheetId="1" r:id="rId1"/>
+    <sheet name="Cust" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="233">
-  <si>
-    <t>Address</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="289">
+  <si>
+    <t>account_number</t>
+  </si>
+  <si>
+    <t>contract_number</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>customer</t>
+  </si>
+  <si>
+    <t>HARARE</t>
+  </si>
+  <si>
+    <t>NULL</t>
   </si>
   <si>
     <t>ZESA HOLDINGS</t>
   </si>
   <si>
-    <t>HARARE</t>
-  </si>
-  <si>
     <t>ZENT HEAD OFFICE</t>
   </si>
   <si>
@@ -69,24 +81,24 @@
     <t>ZPC HEAD OFFICE</t>
   </si>
   <si>
+    <t>HWANGE</t>
+  </si>
+  <si>
     <t>ZPC HWANGE POWER STATION</t>
   </si>
   <si>
-    <t>HWANGE</t>
-  </si>
-  <si>
     <t>ZPC KARIBA</t>
   </si>
   <si>
     <t>ZPC MUNYATI POWER STATION</t>
   </si>
   <si>
+    <t>BULAWAYO</t>
+  </si>
+  <si>
     <t>BULAWAYO NATIONAL TRAINING CENTRE</t>
   </si>
   <si>
-    <t>BULAWAYO</t>
-  </si>
-  <si>
     <t>HESCO</t>
   </si>
   <si>
@@ -144,12 +156,12 @@
     <t>CITY OF HARARE</t>
   </si>
   <si>
+    <t>EASTLEA,HARARE</t>
+  </si>
+  <si>
     <t>CONTITOUCH</t>
   </si>
   <si>
-    <t>EASTLEA,HARARE</t>
-  </si>
-  <si>
     <t>DANDEMUTANDE</t>
   </si>
   <si>
@@ -204,18 +216,18 @@
     <t>JW WILSON INTERNATIONAL (PVT) LTD</t>
   </si>
   <si>
-    <t xml:space="preserve"> Kenac Computer Systems</t>
-  </si>
-  <si>
     <t>Harare</t>
   </si>
   <si>
+    <t>Kenac Computer Systems</t>
+  </si>
+  <si>
+    <t>MARONDERA</t>
+  </si>
+  <si>
     <t>KUSHINGA PHIKELELE</t>
   </si>
   <si>
-    <t>MARONDERA</t>
-  </si>
-  <si>
     <t>LAKAS PRODUCTS (PVT) LTD</t>
   </si>
   <si>
@@ -243,405 +255,408 @@
     <t>NEDBANK ZIMBABWE LIMITED</t>
   </si>
   <si>
+    <t>NETONE CELLULAR</t>
+  </si>
+  <si>
+    <t>NRZ</t>
+  </si>
+  <si>
+    <t>NUST</t>
+  </si>
+  <si>
+    <t>NYARADZO FUNERAL ASSURANCE</t>
+  </si>
+  <si>
+    <t>PARIRENYATWA GRP OF HOSPITALS</t>
+  </si>
+  <si>
+    <t>PETROTRADE</t>
+  </si>
+  <si>
+    <t>POSB</t>
+  </si>
+  <si>
+    <t>PSMAS</t>
+  </si>
+  <si>
+    <t>NYANGANI RENEWABLE ENERGY PVT LTD</t>
+  </si>
+  <si>
+    <t>RESERVE BANK OF ZIMBABWE</t>
+  </si>
+  <si>
+    <t>Rural Electrification Agency</t>
+  </si>
+  <si>
+    <t>SCHWEPPES ZIMBABWE LIMITED</t>
+  </si>
+  <si>
+    <t>TEN TEN TECHNOLOGIES</t>
+  </si>
+  <si>
+    <t>Stanbic Bank Zimbabwe Ltd</t>
+  </si>
+  <si>
+    <t>STARAFRICA OPERATIONS (PVT) LTD</t>
+  </si>
+  <si>
+    <t>TelOne Private Limited</t>
+  </si>
+  <si>
+    <t>Tian Ze Tobacco</t>
+  </si>
+  <si>
+    <t>TM SUPERMARKETS P/L</t>
+  </si>
+  <si>
+    <t>TOBACCO PROCESSORS ZIMBABWE</t>
+  </si>
+  <si>
+    <t>TREGER PRODUCTS (PVT) LTD 1</t>
+  </si>
+  <si>
+    <t>TREGER PRODUCTS (PVT) LTD</t>
+  </si>
+  <si>
+    <t>TSANGA POWER STATION</t>
+  </si>
+  <si>
+    <t>UNIFREIGHT AFRICA LIMITED</t>
+  </si>
+  <si>
+    <t>UNTU CAPITAL</t>
+  </si>
+  <si>
+    <t>VICTORIA FOODS</t>
+  </si>
+  <si>
+    <t>WILLOWVALE VEHICLE BODY ENGINEERING</t>
+  </si>
+  <si>
+    <t>WOMENS UNIVERSITY</t>
+  </si>
+  <si>
+    <t>Z.E.R.A</t>
+  </si>
+  <si>
+    <t>ZB BANK</t>
+  </si>
+  <si>
+    <t>ZIMBABWE ELECTORAL COMMISSION (ZEC)</t>
+  </si>
+  <si>
+    <t>ZFC</t>
+  </si>
+  <si>
+    <t>ZFC SPORTS CLUB</t>
+  </si>
+  <si>
+    <t>ZIMBABWE POSTS</t>
+  </si>
+  <si>
+    <t>ZIMBABWE SHARED SERVICES</t>
+  </si>
+  <si>
+    <t>MUTARE</t>
+  </si>
+  <si>
+    <t>ZIMPAPERS DIAMOND FM</t>
+  </si>
+  <si>
+    <t>ZIMRA</t>
+  </si>
+  <si>
+    <t>ZIMSEC</t>
+  </si>
+  <si>
+    <t>ZIMSWITCH TECHNOLOGIES</t>
+  </si>
+  <si>
+    <t>ZINWA HEAD OFFICE</t>
+  </si>
+  <si>
+    <t>ZUPCO NORTHERN DIVISION</t>
+  </si>
+  <si>
+    <t>ENG N CHIKONYE</t>
+  </si>
+  <si>
+    <t>CALEB TONOENDA CHISWO ZESA HOLDINGS</t>
+  </si>
+  <si>
+    <t>INNOCENT MPOFU</t>
+  </si>
+  <si>
+    <t>NYAKABAU RESIDENCE</t>
+  </si>
+  <si>
+    <t>MAZHAWIDZA  RESIDENCE</t>
+  </si>
+  <si>
+    <t>NYAGURA ADMIRE RINGAI</t>
+  </si>
+  <si>
+    <t>VINCENT KAHIYA</t>
+  </si>
+  <si>
+    <t>FLORENCE MAUNGANIDZE</t>
+  </si>
+  <si>
+    <t>NETSAI TORIRO</t>
+  </si>
+  <si>
+    <t>OLD MUTUAL LIFE ASSURANCE</t>
+  </si>
+  <si>
+    <t>HIT</t>
+  </si>
+  <si>
+    <t>RANGARIRAI MANGUNDU</t>
+  </si>
+  <si>
+    <t>FRAMPOL INVESTMENTS</t>
+  </si>
+  <si>
+    <t>LANCET LABORATORIES (USD)</t>
+  </si>
+  <si>
+    <t>SAPP (USD)</t>
+  </si>
+  <si>
+    <t>ZIMSEC CAR TRACKING ACCOUNT</t>
+  </si>
+  <si>
+    <t>USHE RESIDENCE</t>
+  </si>
+  <si>
+    <t>JESTER MEDIA SERVICES</t>
+  </si>
+  <si>
+    <t>PATRICIA GUMUNYU</t>
+  </si>
+  <si>
+    <t>BRIGHTON MASUNGA</t>
+  </si>
+  <si>
+    <t>CHLORIDE US$</t>
+  </si>
+  <si>
+    <t>SOLUSI UNIVERSITY US$</t>
+  </si>
+  <si>
+    <t>DAIRIBORD US$ ZIMBABWE (PVT) LTD</t>
+  </si>
+  <si>
+    <t>NATIONAL FOODS LTD US$</t>
+  </si>
+  <si>
+    <t>INNBUCKS US$</t>
+  </si>
+  <si>
+    <t>ZIMTILE (PVT) LTD US$</t>
+  </si>
+  <si>
+    <t>SYNTEGRA SOLUTIONS US$</t>
+  </si>
+  <si>
+    <t>OK ZIMBABWE LIMITED</t>
+  </si>
+  <si>
+    <t>Minerals Marketing Corporation</t>
+  </si>
+  <si>
+    <t>HOMELINK US$</t>
+  </si>
+  <si>
+    <t>GWERU</t>
+  </si>
+  <si>
+    <t>DIAGNOSTIC XRAY US$</t>
+  </si>
+  <si>
+    <t>KUDAKWASHE MUZUNZE</t>
+  </si>
+  <si>
+    <t>CYNTHIA NYARADZO US$</t>
+  </si>
+  <si>
+    <t>CHAMPIONS INSURANCE US$</t>
+  </si>
+  <si>
+    <t>AFRICAN EXPORT-IMPORT BANK</t>
+  </si>
+  <si>
+    <t>IMRANA WOLFENDEN</t>
+  </si>
+  <si>
+    <t>WELL WOMAN CLINIC US$</t>
+  </si>
+  <si>
+    <t>CUT RAG PROCESSORS (PVT) LTD</t>
+  </si>
+  <si>
+    <t>DULYS MOTORS</t>
+  </si>
+  <si>
+    <t>OLD MUTUAL FUNERAL SERVICES</t>
+  </si>
+  <si>
+    <t>PG MERCHANDISING US$</t>
+  </si>
+  <si>
+    <t>MUNYATI</t>
+  </si>
+  <si>
+    <t>GENGEZHA EMMANUEL</t>
+  </si>
+  <si>
+    <t>CHITUNGWIZA</t>
+  </si>
+  <si>
+    <t>ADKINS MUDII</t>
+  </si>
+  <si>
+    <t>GETBUCKS</t>
+  </si>
+  <si>
+    <t>SUE MWANZA US$</t>
+  </si>
+  <si>
+    <t>SOLANGE FARIALA</t>
+  </si>
+  <si>
+    <t>RURAL INFRASTRUCTURE DEVELOPMENT AG</t>
+  </si>
+  <si>
+    <t>MUTEMA HIGH SCHOOL</t>
+  </si>
+  <si>
+    <t>SMEDCO US$</t>
+  </si>
+  <si>
+    <t>Astra Paints</t>
+  </si>
+  <si>
+    <t>AXIS SOLUTIONS (PVT) LTD US$</t>
+  </si>
+  <si>
+    <t>TV SALES AND HOME US$</t>
+  </si>
+  <si>
+    <t>ZIMGOLD OIL INDUSTRIES (PVT) LTD</t>
+  </si>
+  <si>
+    <t>POSB INTERNET ACCOUNT</t>
+  </si>
+  <si>
+    <t>GIBBONS LESLEY US$</t>
+  </si>
+  <si>
+    <t>CHIPINGE</t>
+  </si>
+  <si>
+    <t>MWACHETA HIGH SCHOOL US$</t>
+  </si>
+  <si>
+    <t>UNITED BULAWAYO HOSPITAL (UBH)</t>
+  </si>
+  <si>
+    <t>TIMB US$</t>
+  </si>
+  <si>
+    <t>DELTA BEVERAGES (PVT) LTD</t>
+  </si>
+  <si>
+    <t>ZUVA PETROLEUM (PVT) LTD</t>
+  </si>
+  <si>
+    <t>MUTEMA HIGH SCHOOL US$</t>
+  </si>
+  <si>
+    <t>NORTHERN TOBACCO US$</t>
+  </si>
+  <si>
+    <t>EDGARS STORES HQ US$</t>
+  </si>
+  <si>
+    <t>MURINDA LUCKY</t>
+  </si>
+  <si>
+    <t>IT ANYWHERE (PVT) LTD</t>
+  </si>
+  <si>
+    <t>POWERTEL TIN 2000032060</t>
+  </si>
+  <si>
+    <t>PG TIMBERS US$</t>
+  </si>
+  <si>
+    <t>UBC HEALTHCARE US$</t>
+  </si>
+  <si>
+    <t>MINISTRY OF LOCAL GOVERNMENT</t>
+  </si>
+  <si>
+    <t>PHIRI STELLA US$</t>
+  </si>
+  <si>
+    <t>MUTAPA INVESTMENT FUND</t>
+  </si>
+  <si>
+    <t>MASVINGO</t>
+  </si>
+  <si>
+    <t>BIKITA MINERALS (PVT) LIMITED</t>
+  </si>
+  <si>
+    <t>ZIMBABWE PLATINUM MINES PVT LTD US$</t>
+  </si>
+  <si>
+    <t>BARCELONA</t>
+  </si>
+  <si>
+    <t>AFR-IX TELECOMM, S.A.</t>
+  </si>
+  <si>
+    <t>ZIMBABWE RESEARCH AND</t>
+  </si>
+  <si>
+    <t>AJAY MUSLIM BUTCHERY</t>
+  </si>
+  <si>
+    <t>DINSON INDUSTRIAL GROUP ZIMBABWE</t>
+  </si>
+  <si>
+    <t>ZIMBABWE OPEN UNIVERSITY</t>
+  </si>
+  <si>
+    <t>PETROZIM</t>
+  </si>
+  <si>
+    <t>NETONE USD</t>
+  </si>
+  <si>
+    <t>TOCEK ZADZAMATURA</t>
+  </si>
+  <si>
+    <t>INSURANCE COMPANY OF ZIMBABWE</t>
+  </si>
+  <si>
+    <t>ZIMBABWE CENTER FOR HIGHER</t>
+  </si>
+  <si>
+    <t>ALLIED TIMBERS ZIMBABWE</t>
+  </si>
+  <si>
+    <t>HERITAGE SCHOOL</t>
+  </si>
+  <si>
+    <t>National Merchant Bank</t>
+  </si>
+  <si>
     <t>NETONE</t>
   </si>
   <si>
-    <t>NRZ</t>
-  </si>
-  <si>
-    <t>NUST</t>
-  </si>
-  <si>
-    <t>NYARADZO FUNERAL ASSURANCE</t>
-  </si>
-  <si>
-    <t>PARIRENYATWA GRP OF HOSPITALS</t>
-  </si>
-  <si>
-    <t>PETROTRADE</t>
-  </si>
-  <si>
-    <t>POSB</t>
-  </si>
-  <si>
-    <t>PSMAS</t>
-  </si>
-  <si>
-    <t>NYANGANI RENEWABLE ENERGY PVT LTD</t>
-  </si>
-  <si>
-    <t>RESERVE BANK OF ZIMBABWE</t>
-  </si>
-  <si>
-    <t>Rural Electrification Agency</t>
-  </si>
-  <si>
-    <t>SCHWEPPES ZIMBABWE LIMITED</t>
-  </si>
-  <si>
-    <t>TEN TEN TECHNOLOGIES</t>
-  </si>
-  <si>
-    <t>Stanbic Bank Zimbabwe Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Harare</t>
-  </si>
-  <si>
-    <t>STARAFRICA OPERATIONS (PVT) LTD</t>
-  </si>
-  <si>
-    <t>TelOne Private Limited</t>
-  </si>
-  <si>
-    <t>Tian Ze Tobacco</t>
-  </si>
-  <si>
-    <t>TM SUPERMARKETS P/L</t>
-  </si>
-  <si>
-    <t>TOBACCO PROCESSORS ZIMBABWE</t>
-  </si>
-  <si>
-    <t>TREGER PRODUCTS (PVT) LTD</t>
-  </si>
-  <si>
-    <t>TSANGA POWER STATION</t>
-  </si>
-  <si>
-    <t>UNIFREIGHT AFRICA LIMITED</t>
-  </si>
-  <si>
-    <t>UNTU CAPITAL</t>
-  </si>
-  <si>
-    <t>VICTORIA FOODS</t>
-  </si>
-  <si>
-    <t>WILLOWVALE VEHICLE BODY ENGINEERING</t>
-  </si>
-  <si>
-    <t>WOMENS UNIVERSITY</t>
-  </si>
-  <si>
-    <t>Z.E.R.A</t>
-  </si>
-  <si>
-    <t>ZB BANK</t>
-  </si>
-  <si>
-    <t>ZIMBABWE ELECTORAL COMMISSION (ZEC)</t>
-  </si>
-  <si>
-    <t>ZFC</t>
-  </si>
-  <si>
-    <t>ZFC SPORTS CLUB</t>
-  </si>
-  <si>
-    <t>ZIMBABWE POSTS</t>
-  </si>
-  <si>
-    <t>ZIMBABWE SHARED SERVICES</t>
-  </si>
-  <si>
-    <t>ZIMPAPERS DIAMOND FM</t>
-  </si>
-  <si>
-    <t>MUTARE</t>
-  </si>
-  <si>
-    <t>ZIMRA</t>
-  </si>
-  <si>
-    <t>ZIMSEC</t>
-  </si>
-  <si>
-    <t>ZIMSWITCH TECHNOLOGIES</t>
-  </si>
-  <si>
-    <t>ZINWA HEAD OFFICE</t>
-  </si>
-  <si>
-    <t>ZUPCO NORTHERN DIVISION</t>
-  </si>
-  <si>
-    <t>ENG N CHIKONYE</t>
-  </si>
-  <si>
-    <t>CALEB TONOENDA CHISWO ZESA HOLDINGS</t>
-  </si>
-  <si>
-    <t>INNOCENT MPOFU</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NYAKABAU RESIDENCE</t>
-  </si>
-  <si>
-    <t>MAZHAWIDZA  RESIDENCE</t>
-  </si>
-  <si>
-    <t>NYAGURA ADMIRE RINGAI</t>
-  </si>
-  <si>
-    <t>VINCENT KAHIYA</t>
-  </si>
-  <si>
-    <t>FLORENCE MAUNGANIDZE</t>
-  </si>
-  <si>
-    <t>NETSAI TORIRO</t>
-  </si>
-  <si>
-    <t>OLD MUTUAL LIFE ASSURANCE</t>
-  </si>
-  <si>
-    <t>HIT</t>
-  </si>
-  <si>
-    <t>RANGARIRAI MANGUNDU</t>
-  </si>
-  <si>
-    <t>FRAMPOL INVESTMENTS</t>
-  </si>
-  <si>
-    <t>LANCET LABORATORIES (USD)</t>
-  </si>
-  <si>
-    <t>SAPP (USD)</t>
-  </si>
-  <si>
-    <t>ZIMSEC CAR TRACKING ACCOUNT</t>
-  </si>
-  <si>
-    <t>USHE RESIDENCE</t>
-  </si>
-  <si>
-    <t>JESTER MEDIA SERVICES</t>
-  </si>
-  <si>
-    <t>PATRICIA GUMUNYU</t>
-  </si>
-  <si>
-    <t>BRIGHTON MASUNGA</t>
-  </si>
-  <si>
-    <t>CHLORIDE US$</t>
-  </si>
-  <si>
-    <t>SOLUSI UNIVERSITY US$</t>
-  </si>
-  <si>
-    <t>DAIRIBORD US$ ZIMBABWE (PVT) LTD</t>
-  </si>
-  <si>
-    <t>NATIONAL FOODS LTD US$</t>
-  </si>
-  <si>
-    <t>INNBUCKS US$</t>
-  </si>
-  <si>
-    <t>ZIMTILE (PVT) LTD US$</t>
-  </si>
-  <si>
-    <t>SYNTEGRA SOLUTIONS US$</t>
-  </si>
-  <si>
-    <t>OK ZIMBABWE LIMITED</t>
-  </si>
-  <si>
-    <t>Minerals Marketing Corporation</t>
-  </si>
-  <si>
-    <t>HOMELINK US$</t>
-  </si>
-  <si>
-    <t>DIAGNOSTIC XRAY US$</t>
-  </si>
-  <si>
-    <t>GWERU</t>
-  </si>
-  <si>
-    <t>KUDAKWASHE MUZUNZE</t>
-  </si>
-  <si>
-    <t>CYNTHIA NYARADZO US$</t>
-  </si>
-  <si>
-    <t>CHAMPIONS INSURANCE US$</t>
-  </si>
-  <si>
-    <t>AFRICAN EXPORT-IMPORT BANK</t>
-  </si>
-  <si>
-    <t>IMRANA WOLFENDEN</t>
-  </si>
-  <si>
-    <t>WELL WOMAN CLINIC US$</t>
-  </si>
-  <si>
-    <t>CUT RAG PROCESSORS (PVT) LTD</t>
-  </si>
-  <si>
-    <t>DULYS MOTORS</t>
-  </si>
-  <si>
-    <t>OLD MUTUAL FUNERAL SERVICES</t>
-  </si>
-  <si>
-    <t>PG MERCHANDISING US$</t>
-  </si>
-  <si>
-    <t>GENGEZHA EMMANUEL</t>
-  </si>
-  <si>
-    <t>MUNYATI</t>
-  </si>
-  <si>
-    <t>ADKINS MUDII</t>
-  </si>
-  <si>
-    <t>CHITUNGWIZA</t>
-  </si>
-  <si>
-    <t>GETBUCKS</t>
-  </si>
-  <si>
-    <t>SUE MWANZA US$</t>
-  </si>
-  <si>
-    <t>SOLANGE FARIALA</t>
-  </si>
-  <si>
-    <t>RURAL INFRASTRUCTURE DEVELOPMENT AG</t>
-  </si>
-  <si>
-    <t>MUTEMA HIGH SCHOOL</t>
-  </si>
-  <si>
-    <t>SMEDCO US$</t>
-  </si>
-  <si>
-    <t>Astra Paints</t>
-  </si>
-  <si>
-    <t>AXIS SOLUTIONS (PVT) LTD US$</t>
-  </si>
-  <si>
-    <t>TV SALES AND HOME US$</t>
-  </si>
-  <si>
-    <t>ZIMGOLD OIL INDUSTRIES (PVT) LTD</t>
-  </si>
-  <si>
-    <t>POSB INTERNET ACCOUNT</t>
-  </si>
-  <si>
-    <t>GIBBONS LESLEY US$</t>
-  </si>
-  <si>
-    <t>MWACHETA HIGH SCHOOL US$</t>
-  </si>
-  <si>
-    <t>CHIPINGE</t>
-  </si>
-  <si>
-    <t>UNITED BULAWAYO HOSPITAL (UBH)</t>
-  </si>
-  <si>
-    <t>TIMB US$</t>
-  </si>
-  <si>
-    <t>DELTA BEVERAGES (PVT) LTD</t>
-  </si>
-  <si>
-    <t>ZUVA PETROLEUM (PVT) LTD</t>
-  </si>
-  <si>
-    <t>MUTEMA HIGH SCHOOL US$</t>
-  </si>
-  <si>
-    <t>NORTHERN TOBACCO US$</t>
-  </si>
-  <si>
-    <t>EDGARS STORES HQ US$</t>
-  </si>
-  <si>
-    <t>MURINDA LUCKY</t>
-  </si>
-  <si>
-    <t>IT ANYWHERE (PVT) LTD</t>
-  </si>
-  <si>
-    <t>PG TIMBERS US$</t>
-  </si>
-  <si>
-    <t>POWERTEL TIN 2000032060</t>
-  </si>
-  <si>
-    <t>UBC HEALTHCARE US$</t>
-  </si>
-  <si>
-    <t>MINISTRY OF LOCAL GOVERNMENT</t>
-  </si>
-  <si>
-    <t>PHIRI STELLA US$</t>
-  </si>
-  <si>
-    <t>MUTAPA INVESTMENT FUND</t>
-  </si>
-  <si>
-    <t>BIKITA MINERALS (PVT) LIMITED</t>
-  </si>
-  <si>
-    <t>MASVINGO</t>
-  </si>
-  <si>
-    <t>ZIMBABWE PLATINUM MINES PVT LTD US$</t>
-  </si>
-  <si>
-    <t>AFR-IX TELECOMM, S.A.</t>
-  </si>
-  <si>
-    <t>BARCELONA</t>
-  </si>
-  <si>
-    <t>ZIMBABWE RESEARCH AND</t>
-  </si>
-  <si>
-    <t>AJAY MUSLIM BUTCHERY</t>
-  </si>
-  <si>
-    <t>DINSON INDUSTRIAL GROUP ZIMBABWE</t>
-  </si>
-  <si>
-    <t>ZIMBABWE OPEN UNIVERSITY</t>
-  </si>
-  <si>
-    <t>PETROZIM</t>
-  </si>
-  <si>
-    <t>NETONE USD</t>
-  </si>
-  <si>
-    <t>TOCEK ZADZAMATURA</t>
-  </si>
-  <si>
-    <t>INSURANCE COMPANY OF ZIMBABWE</t>
-  </si>
-  <si>
-    <t>ZIMBABWE CENTER FOR HIGHER</t>
-  </si>
-  <si>
-    <t>ALLIED TIMBERS ZIMBABWE</t>
-  </si>
-  <si>
-    <t>HERITAGE SCHOOL</t>
-  </si>
-  <si>
-    <t>National Merchant Bank</t>
-  </si>
-  <si>
     <t>OLD MUTUAL INSURANCE COMPANY</t>
   </si>
   <si>
@@ -663,12 +678,12 @@
     <t>BancABC ZW</t>
   </si>
   <si>
+    <t>SELOUS</t>
+  </si>
+  <si>
     <t>ZIMBABWE PLATINUM MINES PVT LTD</t>
   </si>
   <si>
-    <t>SELOUS</t>
-  </si>
-  <si>
     <t>INSTITUTE OF CORPORATE DIRECTORS ZI</t>
   </si>
   <si>
@@ -696,7 +711,7 @@
     <t>MASOTSHA PRIMARY SCHOOL</t>
   </si>
   <si>
-    <t>CHARLSE SHOKOBISHI</t>
+    <t>CHARLES SHOKOBISHI</t>
   </si>
   <si>
     <t>ZUPCO SOUTHERN DIVISION ZWG</t>
@@ -711,13 +726,166 @@
     <t>TAFARA CHARUMBIRA</t>
   </si>
   <si>
-    <t>customer</t>
-  </si>
-  <si>
-    <t>contract_number</t>
-  </si>
-  <si>
-    <t>account_number</t>
+    <t>FORBES BOARDER POST MUTARE</t>
+  </si>
+  <si>
+    <t>GARSU PASAULIS</t>
+  </si>
+  <si>
+    <t>100 L Takawira St</t>
+  </si>
+  <si>
+    <t>NOIC ZIM</t>
+  </si>
+  <si>
+    <t>21 BIRMINGHAM ROAD, SOUTHERTON</t>
+  </si>
+  <si>
+    <t>TENDO ELECTRONICS (PVT) LTD</t>
+  </si>
+  <si>
+    <t>NO. 3 GENERAL BOOTH ROAD,BRAES</t>
+  </si>
+  <si>
+    <t>MOIRA JOSEPH</t>
+  </si>
+  <si>
+    <t>HOUSE 16 ZESA BROMLEY</t>
+  </si>
+  <si>
+    <t>TRACY MUNDORINGISA</t>
+  </si>
+  <si>
+    <t>HSE NO 13 EAST ROAD, MUNYATI</t>
+  </si>
+  <si>
+    <t>MOYO WAYNE MILES</t>
+  </si>
+  <si>
+    <t>HOUSE NO 158 CHIMWENDO, MUNYATI</t>
+  </si>
+  <si>
+    <t>CHINGOLI KNOWLEDGE</t>
+  </si>
+  <si>
+    <t>19176 RIDGEVIEW BELVEDERE</t>
+  </si>
+  <si>
+    <t>MICHAEL KASEKE</t>
+  </si>
+  <si>
+    <t>33 EASTEND,MUNYATI</t>
+  </si>
+  <si>
+    <t>SITHOLE SILAS MAMUTI</t>
+  </si>
+  <si>
+    <t>57 LEORYOD ROAD BRAESIDE</t>
+  </si>
+  <si>
+    <t>KASEKE TRIFORDHAMAN</t>
+  </si>
+  <si>
+    <t>52 SOMERSET DRIVE EASTLEA</t>
+  </si>
+  <si>
+    <t>ALLIED INSURANCE</t>
+  </si>
+  <si>
+    <t>11592 TAFARA WAY KAMUNHU SHOPS,MABVUKU</t>
+  </si>
+  <si>
+    <t>PACIFIC 24HR HOSPITAL</t>
+  </si>
+  <si>
+    <t>SIRDC</t>
+  </si>
+  <si>
+    <t>MAGWAZA MERCY</t>
+  </si>
+  <si>
+    <t>68 NELSON MANDELA AVENUE</t>
+  </si>
+  <si>
+    <t>CROWN BANK</t>
+  </si>
+  <si>
+    <t>1381 NHUTA CLOSE HOUGHTON PARK</t>
+  </si>
+  <si>
+    <t>PHIRI STELLA</t>
+  </si>
+  <si>
+    <t>2 TUDLEY ROAD, MT PLEASANT</t>
+  </si>
+  <si>
+    <t>GISP</t>
+  </si>
+  <si>
+    <t>4 PARK STREET</t>
+  </si>
+  <si>
+    <t>TRAFFIC SAFETY COUNCIL OF ZIMB</t>
+  </si>
+  <si>
+    <t>7967 COWIE RD COLD COMFORT</t>
+  </si>
+  <si>
+    <t>CHIEDZA TANGADZANI</t>
+  </si>
+  <si>
+    <t>8025 COLD COMFORT</t>
+  </si>
+  <si>
+    <t>SARAH PASI</t>
+  </si>
+  <si>
+    <t>8043 COLD COMFORT</t>
+  </si>
+  <si>
+    <t>UNITY CHIBAKWE</t>
+  </si>
+  <si>
+    <t>5 BARK ROAD, WILLOVALE</t>
+  </si>
+  <si>
+    <t>SABENI INTERCONNECT</t>
+  </si>
+  <si>
+    <t>18 SWIPE ROAD , MT PLEASENT</t>
+  </si>
+  <si>
+    <t>ANELE MOYO</t>
+  </si>
+  <si>
+    <t>14633 COLD COMFORT</t>
+  </si>
+  <si>
+    <t>TONDERAI MAPAIKE</t>
+  </si>
+  <si>
+    <t>8123 COLD COMFORT</t>
+  </si>
+  <si>
+    <t>YVONNE SAITI</t>
+  </si>
+  <si>
+    <t>7962 COWIE ROAD COLD COMFORT</t>
+  </si>
+  <si>
+    <t>LAWRENCE RIMAYI</t>
+  </si>
+  <si>
+    <t>15030 COLD COMFORT</t>
+  </si>
+  <si>
+    <t>BRIAN CHITANHA</t>
+  </si>
+  <si>
+    <t>4 CONALD ROAD GRANITESIDE</t>
+  </si>
+  <si>
+    <t>TRUWORTHS LIMITED</t>
   </si>
 </sst>
 </file>
@@ -1524,27 +1692,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D219"/>
+  <dimension ref="A1:D244"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" customWidth="1"/>
-    <col min="3" max="3" width="38.88671875" customWidth="1"/>
-    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="1" max="1" width="27.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>231</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>230</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1552,2931 +1717,3281 @@
         <v>700000001</v>
       </c>
       <c r="B2">
-        <v>40108560</v>
+        <v>40108561</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>700000001</v>
+        <v>700000361</v>
       </c>
       <c r="B3">
-        <v>40108561</v>
+        <v>40108559</v>
       </c>
       <c r="C3" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>700000361</v>
+        <v>700000362</v>
       </c>
       <c r="B4">
-        <v>40108559</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
+        <v>40108562</v>
       </c>
       <c r="D4" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>700000362</v>
+        <v>700000363</v>
       </c>
       <c r="B5">
-        <v>40108562</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
+        <v>40108564</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>700000363</v>
+        <v>700000365</v>
       </c>
       <c r="B6">
-        <v>40108564</v>
+        <v>40108566</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>700000365</v>
+        <v>700000366</v>
       </c>
       <c r="B7">
-        <v>40108566</v>
+        <v>40108568</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>700000366</v>
+        <v>700000367</v>
       </c>
       <c r="B8">
-        <v>40108568</v>
+        <v>40092352</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>700000367</v>
+        <v>700000368</v>
       </c>
       <c r="B9">
-        <v>40092352</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
+        <v>40098802</v>
       </c>
       <c r="D9" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>700000368</v>
+        <v>700000370</v>
       </c>
       <c r="B10">
-        <v>40098802</v>
+        <v>40101692</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>700000370</v>
+        <v>700000371</v>
       </c>
       <c r="B11">
-        <v>40101692</v>
+        <v>40108570</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>700000371</v>
+        <v>700000372</v>
       </c>
       <c r="B12">
-        <v>40108570</v>
+        <v>40108572</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>700000372</v>
+        <v>700000373</v>
       </c>
       <c r="B13">
-        <v>40108572</v>
+        <v>40108575</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>700000373</v>
+        <v>700000374</v>
       </c>
       <c r="B14">
-        <v>40108575</v>
-      </c>
-      <c r="C14" t="s">
-        <v>13</v>
+        <v>40108577</v>
       </c>
       <c r="D14" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>700000374</v>
+        <v>700000375</v>
       </c>
       <c r="B15">
-        <v>40108577</v>
+        <v>40108580</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>700000375</v>
+        <v>700000376</v>
       </c>
       <c r="B16">
-        <v>40108580</v>
+        <v>40108584</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>700000376</v>
+        <v>700000401</v>
       </c>
       <c r="B17">
-        <v>40108584</v>
+        <v>40092373</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>700000401</v>
+        <v>700000407</v>
       </c>
       <c r="B18">
-        <v>40092373</v>
-      </c>
-      <c r="C18" t="s">
-        <v>18</v>
+        <v>40108587</v>
       </c>
       <c r="D18" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>700000407</v>
+        <v>700000462</v>
       </c>
       <c r="B19">
-        <v>40108587</v>
+        <v>40100718</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>700000462</v>
+        <v>700000471</v>
       </c>
       <c r="B20">
-        <v>40100718</v>
+        <v>40100725</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>700000471</v>
+        <v>700000476</v>
       </c>
       <c r="B21">
-        <v>40100725</v>
+        <v>40101698</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>700000476</v>
+        <v>1200000005</v>
       </c>
       <c r="B22">
-        <v>40101698</v>
-      </c>
-      <c r="C22" t="s">
-        <v>23</v>
+        <v>40098813</v>
       </c>
       <c r="D22" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>1200000005</v>
+        <v>1200000017</v>
       </c>
       <c r="B23">
-        <v>40098813</v>
-      </c>
-      <c r="C23" t="s">
-        <v>24</v>
+        <v>40092362</v>
+      </c>
+      <c r="D23" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>1200000017</v>
+        <v>1200000032</v>
       </c>
       <c r="B24">
-        <v>40092362</v>
-      </c>
-      <c r="C24" t="s">
-        <v>25</v>
+        <v>40108589</v>
+      </c>
+      <c r="D24" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>1200000032</v>
+        <v>1200000044</v>
       </c>
       <c r="B25">
-        <v>40108589</v>
+        <v>40108591</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>1200000044</v>
+        <v>1200000055</v>
       </c>
       <c r="B26">
-        <v>40108591</v>
+        <v>40108595</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>1200000055</v>
+        <v>1200000077</v>
       </c>
       <c r="B27">
-        <v>40108595</v>
+        <v>40092252</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>1200000077</v>
+        <v>1200000079</v>
       </c>
       <c r="B28">
-        <v>40092252</v>
+        <v>40092417</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>1200000079</v>
+        <v>1200000094</v>
       </c>
       <c r="B29">
-        <v>40092417</v>
+        <v>40092150</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>1200000094</v>
+        <v>1200000128</v>
       </c>
       <c r="B30">
-        <v>40092150</v>
+        <v>40108600</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>1200000128</v>
+        <v>1200000131</v>
       </c>
       <c r="B31">
-        <v>40108600</v>
+        <v>40108602</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>1200000131</v>
+        <v>1200000136</v>
       </c>
       <c r="B32">
-        <v>40108602</v>
+        <v>40108604</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>1200000136</v>
+        <v>1200000137</v>
       </c>
       <c r="B33">
-        <v>40108604</v>
+        <v>40100721</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>1200000137</v>
+        <v>1200000153</v>
       </c>
       <c r="B34">
-        <v>40100721</v>
+        <v>40108674</v>
       </c>
       <c r="C34" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>1200000153</v>
+        <v>1200000155</v>
       </c>
       <c r="B35">
-        <v>40108674</v>
+        <v>40108605</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>1200000155</v>
+        <v>1200000167</v>
       </c>
       <c r="B36">
-        <v>40108605</v>
+        <v>40108608</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>1200000167</v>
+        <v>1200000174</v>
       </c>
       <c r="B37">
-        <v>40108608</v>
+        <v>40108612</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>1200000174</v>
+        <v>1200000181</v>
       </c>
       <c r="B38">
-        <v>40108612</v>
-      </c>
-      <c r="C38" t="s">
-        <v>39</v>
+        <v>40108614</v>
       </c>
       <c r="D38" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>1200000181</v>
+        <v>1200000197</v>
       </c>
       <c r="B39">
-        <v>40108614</v>
+        <v>40108622</v>
       </c>
       <c r="C39" t="s">
-        <v>40</v>
+        <v>45</v>
+      </c>
+      <c r="D39" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>1200000197</v>
+        <v>1200000220</v>
       </c>
       <c r="B40">
-        <v>40108622</v>
+        <v>40100717</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>1200000220</v>
+        <v>1200000240</v>
       </c>
       <c r="B41">
-        <v>40100717</v>
+        <v>40108624</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>1200000240</v>
+        <v>1200000248</v>
       </c>
       <c r="B42">
-        <v>40108624</v>
+        <v>40108636</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>1200000248</v>
+        <v>1200000249</v>
       </c>
       <c r="B43">
-        <v>40108636</v>
+        <v>40108631</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>1200000249</v>
+        <v>1200000252</v>
       </c>
       <c r="B44">
-        <v>40108631</v>
+        <v>40108646</v>
       </c>
       <c r="C44" t="s">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>1200000252</v>
+        <v>1200000256</v>
       </c>
       <c r="B45">
-        <v>40108646</v>
+        <v>40108649</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>1200000256</v>
+        <v>1200000258</v>
       </c>
       <c r="B46">
-        <v>40108649</v>
+        <v>40092429</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>1200000258</v>
+        <v>1200000274</v>
       </c>
       <c r="B47">
-        <v>40092429</v>
+        <v>40092459</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>1200000274</v>
+        <v>1200000278</v>
       </c>
       <c r="B48">
-        <v>40092459</v>
+        <v>40108650</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>1200000278</v>
+        <v>1200000281</v>
       </c>
       <c r="B49">
-        <v>40108650</v>
+        <v>40108652</v>
       </c>
       <c r="C49" t="s">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>1200000281</v>
+        <v>1200000285</v>
       </c>
       <c r="B50">
-        <v>40108652</v>
+        <v>40108653</v>
       </c>
       <c r="C50" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>1200000285</v>
+        <v>1200000287</v>
       </c>
       <c r="B51">
-        <v>40108653</v>
+        <v>40108658</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>1200000287</v>
+        <v>1200000317</v>
       </c>
       <c r="B52">
-        <v>40108658</v>
+        <v>40092413</v>
       </c>
       <c r="C52" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>1200000317</v>
+        <v>1200000351</v>
       </c>
       <c r="B53">
-        <v>40092413</v>
+        <v>40108661</v>
       </c>
       <c r="C53" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>1200000351</v>
+        <v>1200000355</v>
       </c>
       <c r="B54">
-        <v>40108661</v>
+        <v>40108663</v>
       </c>
       <c r="C54" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>2</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>1200000355</v>
+        <v>1200000358</v>
       </c>
       <c r="B55">
-        <v>40108663</v>
+        <v>40108664</v>
       </c>
       <c r="C55" t="s">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>2</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>1200000358</v>
+        <v>1200000362</v>
       </c>
       <c r="B56">
-        <v>40108664</v>
+        <v>40092296</v>
       </c>
       <c r="C56" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>1200000362</v>
+        <v>1200000391</v>
       </c>
       <c r="B57">
-        <v>40092296</v>
+        <v>40108665</v>
       </c>
       <c r="C57" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>1200000391</v>
+        <v>1200000397</v>
       </c>
       <c r="B58">
-        <v>40108665</v>
+        <v>40108666</v>
       </c>
       <c r="C58" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D58" t="s">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>1200000397</v>
+        <v>1200000405</v>
       </c>
       <c r="B59">
-        <v>40108666</v>
+        <v>40092678</v>
       </c>
       <c r="C59" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D59" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>1200000405</v>
+        <v>1200000412</v>
       </c>
       <c r="B60">
-        <v>40092678</v>
+        <v>40108667</v>
       </c>
       <c r="C60" t="s">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>1200000412</v>
+        <v>1200000418</v>
       </c>
       <c r="B61">
-        <v>40108667</v>
+        <v>40108668</v>
       </c>
       <c r="C61" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>2</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>1200000418</v>
+        <v>1200000469</v>
       </c>
       <c r="B62">
-        <v>40108668</v>
+        <v>40108670</v>
       </c>
       <c r="C62" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>2</v>
+        <v>71</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>1200000469</v>
+        <v>1200000483</v>
       </c>
       <c r="B63">
-        <v>40108670</v>
+        <v>40108662</v>
       </c>
       <c r="C63" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>2</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>1200000483</v>
+        <v>1200000516</v>
       </c>
       <c r="B64">
-        <v>40108662</v>
+        <v>40108660</v>
       </c>
       <c r="C64" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>2</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>1200000516</v>
+        <v>1200000522</v>
       </c>
       <c r="B65">
-        <v>40108660</v>
+        <v>40092199</v>
       </c>
       <c r="C65" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>1200000522</v>
+        <v>1200000526</v>
       </c>
       <c r="B66">
-        <v>40092199</v>
+        <v>40108657</v>
       </c>
       <c r="C66" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>1200000526</v>
+        <v>1200000528</v>
       </c>
       <c r="B67">
-        <v>40108657</v>
+        <v>40108656</v>
       </c>
       <c r="C67" t="s">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>2</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>1200000528</v>
+        <v>1200000533</v>
       </c>
       <c r="B68">
-        <v>40108656</v>
+        <v>40092337</v>
       </c>
       <c r="C68" t="s">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>2</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>1200000533</v>
+        <v>1200000537</v>
       </c>
       <c r="B69">
-        <v>40092337</v>
+        <v>40102668</v>
       </c>
       <c r="C69" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>1200000537</v>
+        <v>1200000553</v>
       </c>
       <c r="B70">
-        <v>40102668</v>
+        <v>40108655</v>
       </c>
       <c r="C70" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>2</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>1200000553</v>
+        <v>1200000556</v>
       </c>
       <c r="B71">
-        <v>40108655</v>
+        <v>40108654</v>
       </c>
       <c r="C71" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="D71" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>1200000556</v>
+        <v>1200000557</v>
       </c>
       <c r="B72">
-        <v>40108654</v>
+        <v>40108651</v>
       </c>
       <c r="C72" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>1200000557</v>
+        <v>1200000571</v>
       </c>
       <c r="B73">
-        <v>40108651</v>
+        <v>40108648</v>
       </c>
       <c r="C73" t="s">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>2</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>1200000571</v>
+        <v>1200000580</v>
       </c>
       <c r="B74">
-        <v>40108648</v>
+        <v>40108647</v>
       </c>
       <c r="C74" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>2</v>
+        <v>83</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>1200000580</v>
+        <v>1200000597</v>
       </c>
       <c r="B75">
-        <v>40108647</v>
+        <v>40108569</v>
       </c>
       <c r="C75" t="s">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>1200000597</v>
+        <v>1200000608</v>
       </c>
       <c r="B76">
-        <v>40108569</v>
+        <v>40108645</v>
       </c>
       <c r="C76" t="s">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>1200000608</v>
+        <v>1200000614</v>
       </c>
       <c r="B77">
-        <v>40108645</v>
-      </c>
-      <c r="C77" t="s">
-        <v>81</v>
+        <v>40108644</v>
       </c>
       <c r="D77" t="s">
-        <v>2</v>
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>1200000614</v>
+        <v>1200000634</v>
       </c>
       <c r="B78">
-        <v>40108644</v>
+        <v>40108643</v>
       </c>
       <c r="C78" t="s">
-        <v>82</v>
+        <v>4</v>
+      </c>
+      <c r="D78" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>1200000634</v>
+        <v>1200000642</v>
       </c>
       <c r="B79">
-        <v>40108643</v>
+        <v>40108642</v>
       </c>
       <c r="C79" t="s">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>1200000642</v>
+        <v>1200000661</v>
       </c>
       <c r="B80">
-        <v>40108642</v>
+        <v>40108641</v>
       </c>
       <c r="C80" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="D80" t="s">
-        <v>2</v>
+        <v>89</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>1200000661</v>
+        <v>1200000687</v>
       </c>
       <c r="B81">
-        <v>40108641</v>
+        <v>40108640</v>
       </c>
       <c r="C81" t="s">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="D81" t="s">
-        <v>2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>1200000687</v>
+        <v>1200000697</v>
       </c>
       <c r="B82">
-        <v>40108640</v>
+        <v>40108677</v>
       </c>
       <c r="C82" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="D82" t="s">
-        <v>2</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>1200000697</v>
+        <v>1200000701</v>
       </c>
       <c r="B83">
-        <v>40108677</v>
+        <v>40108639</v>
       </c>
       <c r="C83" t="s">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="D83" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>1200000701</v>
+        <v>1200000728</v>
       </c>
       <c r="B84">
-        <v>40108639</v>
+        <v>40092144</v>
       </c>
       <c r="C84" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="D84" t="s">
-        <v>2</v>
+        <v>93</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>1200000728</v>
+        <v>1200000739</v>
       </c>
       <c r="B85">
-        <v>40092144</v>
+        <v>40100723</v>
       </c>
       <c r="C85" t="s">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="D85" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>1200000739</v>
+        <v>1200000743</v>
       </c>
       <c r="B86">
-        <v>40100723</v>
+        <v>40108638</v>
       </c>
       <c r="C86" t="s">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="D86" t="s">
-        <v>2</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>1200000743</v>
+        <v>1200000744</v>
       </c>
       <c r="B87">
-        <v>40108638</v>
+        <v>40108688</v>
       </c>
       <c r="C87" t="s">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="D87" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>1200000744</v>
+        <v>1200000755</v>
       </c>
       <c r="B88">
-        <v>40108688</v>
+        <v>40108637</v>
       </c>
       <c r="C88" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="D88" t="s">
-        <v>2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>1200000755</v>
+        <v>1200000756</v>
       </c>
       <c r="B89">
-        <v>40108637</v>
+        <v>40108635</v>
       </c>
       <c r="C89" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="D89" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>1200000756</v>
+        <v>1200000766</v>
       </c>
       <c r="B90">
-        <v>40108635</v>
-      </c>
-      <c r="C90" t="s">
-        <v>94</v>
+        <v>40108634</v>
       </c>
       <c r="D90" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>1200000766</v>
+        <v>1200000777</v>
       </c>
       <c r="B91">
-        <v>40108634</v>
+        <v>40108633</v>
       </c>
       <c r="C91" t="s">
-        <v>95</v>
+        <v>4</v>
+      </c>
+      <c r="D91" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>1200000777</v>
+        <v>1200000782</v>
       </c>
       <c r="B92">
-        <v>40108633</v>
+        <v>40108632</v>
       </c>
       <c r="C92" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="D92" t="s">
-        <v>2</v>
+        <v>101</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>1200000782</v>
+        <v>1200000803</v>
       </c>
       <c r="B93">
-        <v>40108632</v>
+        <v>40092449</v>
       </c>
       <c r="C93" t="s">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="D93" t="s">
-        <v>2</v>
+        <v>102</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>1200000803</v>
+        <v>1200000826</v>
       </c>
       <c r="B94">
-        <v>40092449</v>
+        <v>40108630</v>
       </c>
       <c r="C94" t="s">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="D94" t="s">
-        <v>2</v>
+        <v>103</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>1200000826</v>
+        <v>1200000828</v>
       </c>
       <c r="B95">
-        <v>40108630</v>
+        <v>40108629</v>
       </c>
       <c r="C95" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="D95" t="s">
-        <v>2</v>
+        <v>104</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>1200000828</v>
+        <v>1200000838</v>
       </c>
       <c r="B96">
-        <v>40108629</v>
-      </c>
-      <c r="C96" t="s">
-        <v>100</v>
+        <v>40108628</v>
       </c>
       <c r="D96" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>1200000838</v>
+        <v>1200000843</v>
       </c>
       <c r="B97">
-        <v>40108628</v>
+        <v>40092491</v>
       </c>
       <c r="C97" t="s">
-        <v>101</v>
+        <v>4</v>
+      </c>
+      <c r="D97" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>1200000843</v>
+        <v>1200000847</v>
       </c>
       <c r="B98">
-        <v>40092491</v>
+        <v>40108627</v>
       </c>
       <c r="C98" t="s">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="D98" t="s">
-        <v>2</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>1200000847</v>
+        <v>1200000855</v>
       </c>
       <c r="B99">
-        <v>40108627</v>
+        <v>40108625</v>
       </c>
       <c r="C99" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="D99" t="s">
-        <v>2</v>
+        <v>108</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>1200000855</v>
+        <v>1200000856</v>
       </c>
       <c r="B100">
-        <v>40108625</v>
+        <v>40108626</v>
       </c>
       <c r="C100" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="D100" t="s">
-        <v>2</v>
+        <v>109</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>1200000856</v>
+        <v>1200000873</v>
       </c>
       <c r="B101">
-        <v>40108626</v>
+        <v>40108623</v>
       </c>
       <c r="C101" t="s">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="D101" t="s">
-        <v>2</v>
+        <v>110</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>1200000873</v>
+        <v>1200000876</v>
       </c>
       <c r="B102">
-        <v>40108623</v>
+        <v>40108621</v>
       </c>
       <c r="C102" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="D102" t="s">
-        <v>2</v>
+        <v>111</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>1200000876</v>
+        <v>1200000885</v>
       </c>
       <c r="B103">
-        <v>40108621</v>
+        <v>40108620</v>
       </c>
       <c r="C103" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D103" t="s">
-        <v>2</v>
+        <v>113</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>1200000885</v>
+        <v>1200000888</v>
       </c>
       <c r="B104">
-        <v>40108620</v>
-      </c>
-      <c r="C104" t="s">
-        <v>108</v>
+        <v>40108676</v>
       </c>
       <c r="D104" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>1200000888</v>
+        <v>1200000889</v>
       </c>
       <c r="B105">
-        <v>40108676</v>
+        <v>40108673</v>
       </c>
       <c r="C105" t="s">
-        <v>110</v>
+        <v>4</v>
+      </c>
+      <c r="D105" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>1200000889</v>
+        <v>1200000892</v>
       </c>
       <c r="B106">
-        <v>40108673</v>
+        <v>40108617</v>
       </c>
       <c r="C106" t="s">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="D106" t="s">
-        <v>2</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>1200000892</v>
+        <v>1200000895</v>
       </c>
       <c r="B107">
-        <v>40108617</v>
-      </c>
-      <c r="C107" t="s">
-        <v>112</v>
+        <v>40108615</v>
       </c>
       <c r="D107" t="s">
-        <v>2</v>
+        <v>117</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>1200000895</v>
+        <v>1200000906</v>
       </c>
       <c r="B108">
-        <v>40108615</v>
+        <v>40108613</v>
       </c>
       <c r="C108" t="s">
-        <v>113</v>
+        <v>4</v>
+      </c>
+      <c r="D108" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>1200000906</v>
+        <v>1200000916</v>
       </c>
       <c r="B109">
-        <v>40108613</v>
-      </c>
-      <c r="C109" t="s">
-        <v>114</v>
+        <v>40092318</v>
       </c>
       <c r="D109" t="s">
-        <v>2</v>
+        <v>119</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>1200000916</v>
+        <v>1200000931</v>
       </c>
       <c r="B110">
-        <v>40092318</v>
+        <v>40092184</v>
       </c>
       <c r="C110" t="s">
-        <v>115</v>
+        <v>4</v>
+      </c>
+      <c r="D110" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>1200000931</v>
+        <v>1200001022</v>
       </c>
       <c r="B111">
-        <v>40092184</v>
+        <v>40092403</v>
       </c>
       <c r="C111" t="s">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="D111" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>1200001022</v>
+        <v>1200001023</v>
       </c>
       <c r="B112">
-        <v>40092403</v>
+        <v>40108611</v>
       </c>
       <c r="C112" t="s">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="D112" t="s">
-        <v>2</v>
+        <v>122</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>1200001023</v>
+        <v>1200001253</v>
       </c>
       <c r="B113">
-        <v>40108611</v>
+        <v>40100700</v>
       </c>
       <c r="C113" t="s">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="D113" t="s">
-        <v>2</v>
+        <v>123</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>1200001253</v>
+        <v>1200001445</v>
       </c>
       <c r="B114">
-        <v>40100700</v>
+        <v>40097847</v>
       </c>
       <c r="C114" t="s">
-        <v>119</v>
+        <v>4</v>
       </c>
       <c r="D114" t="s">
-        <v>2</v>
+        <v>124</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>1200001445</v>
+        <v>1200001637</v>
       </c>
       <c r="B115">
-        <v>40097847</v>
+        <v>40098794</v>
       </c>
       <c r="C115" t="s">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="D115" t="s">
-        <v>2</v>
+        <v>125</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>1200001637</v>
+        <v>1200001665</v>
       </c>
       <c r="B116">
-        <v>40098794</v>
-      </c>
-      <c r="C116" t="s">
-        <v>121</v>
+        <v>40092325</v>
       </c>
       <c r="D116" t="s">
-        <v>2</v>
+        <v>126</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>1200001665</v>
+        <v>1200001670</v>
       </c>
       <c r="B117">
-        <v>40092325</v>
+        <v>40108610</v>
       </c>
       <c r="C117" t="s">
-        <v>122</v>
+        <v>4</v>
+      </c>
+      <c r="D117" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>1200001670</v>
+        <v>1200001785</v>
       </c>
       <c r="B118">
-        <v>40108610</v>
+        <v>40092253</v>
       </c>
       <c r="C118" t="s">
-        <v>123</v>
+        <v>4</v>
       </c>
       <c r="D118" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>1200001785</v>
+        <v>1200001789</v>
       </c>
       <c r="B119">
-        <v>40092253</v>
+        <v>40108609</v>
       </c>
       <c r="C119" t="s">
-        <v>124</v>
+        <v>4</v>
       </c>
       <c r="D119" t="s">
-        <v>2</v>
+        <v>129</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>1200001789</v>
+        <v>1200001858</v>
       </c>
       <c r="B120">
-        <v>40108609</v>
+        <v>40108607</v>
       </c>
       <c r="C120" t="s">
-        <v>125</v>
+        <v>4</v>
       </c>
       <c r="D120" t="s">
-        <v>2</v>
+        <v>130</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>1200001858</v>
+        <v>1200001871</v>
       </c>
       <c r="B121">
-        <v>40108607</v>
+        <v>40102666</v>
       </c>
       <c r="C121" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="D121" t="s">
-        <v>2</v>
+        <v>131</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122">
-        <v>1200001871</v>
+        <v>1200001876</v>
       </c>
       <c r="B122">
-        <v>40102666</v>
+        <v>40101693</v>
       </c>
       <c r="C122" t="s">
-        <v>127</v>
+        <v>4</v>
       </c>
       <c r="D122" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>1200001876</v>
+        <v>1200001877</v>
       </c>
       <c r="B123">
-        <v>40101693</v>
+        <v>40108606</v>
       </c>
       <c r="C123" t="s">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="D123" t="s">
-        <v>2</v>
+        <v>133</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>1200001877</v>
+        <v>1200001881</v>
       </c>
       <c r="B124">
-        <v>40108606</v>
+        <v>40108619</v>
       </c>
       <c r="C124" t="s">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="D124" t="s">
-        <v>2</v>
+        <v>134</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>1200001881</v>
+        <v>1200001896</v>
       </c>
       <c r="B125">
-        <v>40108619</v>
+        <v>40100701</v>
       </c>
       <c r="C125" t="s">
-        <v>130</v>
+        <v>4</v>
       </c>
       <c r="D125" t="s">
-        <v>2</v>
+        <v>135</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>1200001896</v>
+        <v>1200001899</v>
       </c>
       <c r="B126">
-        <v>40100701</v>
+        <v>40108603</v>
       </c>
       <c r="C126" t="s">
-        <v>131</v>
+        <v>4</v>
       </c>
       <c r="D126" t="s">
-        <v>2</v>
+        <v>136</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>1200001899</v>
+        <v>1200001917</v>
       </c>
       <c r="B127">
-        <v>40108603</v>
+        <v>40103643</v>
       </c>
       <c r="C127" t="s">
-        <v>132</v>
+        <v>4</v>
       </c>
       <c r="D127" t="s">
-        <v>2</v>
+        <v>137</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>1200001917</v>
+        <v>1200001918</v>
       </c>
       <c r="B128">
-        <v>40103643</v>
+        <v>40108558</v>
       </c>
       <c r="C128" t="s">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="D128" t="s">
-        <v>2</v>
+        <v>138</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>1200001918</v>
+        <v>1200001940</v>
       </c>
       <c r="B129">
-        <v>40108558</v>
+        <v>40108686</v>
       </c>
       <c r="C129" t="s">
-        <v>134</v>
+        <v>4</v>
       </c>
       <c r="D129" t="s">
-        <v>2</v>
+        <v>139</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>1200001940</v>
+        <v>1200001967</v>
       </c>
       <c r="B130">
-        <v>40108686</v>
-      </c>
-      <c r="C130" t="s">
-        <v>135</v>
+        <v>40108601</v>
       </c>
       <c r="D130" t="s">
-        <v>2</v>
+        <v>140</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>1200001967</v>
+        <v>1200001968</v>
       </c>
       <c r="B131">
-        <v>40108601</v>
+        <v>40108599</v>
       </c>
       <c r="C131" t="s">
-        <v>136</v>
+        <v>4</v>
+      </c>
+      <c r="D131" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132">
-        <v>1200001968</v>
+        <v>1200001969</v>
       </c>
       <c r="B132">
-        <v>40108599</v>
-      </c>
-      <c r="C132" t="s">
-        <v>137</v>
+        <v>40108598</v>
       </c>
       <c r="D132" t="s">
-        <v>2</v>
+        <v>142</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133">
-        <v>1200001969</v>
+        <v>1200001971</v>
       </c>
       <c r="B133">
-        <v>40108598</v>
+        <v>40108596</v>
       </c>
       <c r="C133" t="s">
-        <v>138</v>
+        <v>4</v>
+      </c>
+      <c r="D133" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134">
-        <v>1200001971</v>
+        <v>1200001981</v>
       </c>
       <c r="B134">
-        <v>40108596</v>
-      </c>
-      <c r="C134" t="s">
-        <v>139</v>
+        <v>40108594</v>
       </c>
       <c r="D134" t="s">
-        <v>2</v>
+        <v>144</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135">
-        <v>1200001981</v>
+        <v>1200001984</v>
       </c>
       <c r="B135">
-        <v>40108594</v>
+        <v>40108593</v>
       </c>
       <c r="C135" t="s">
-        <v>140</v>
+        <v>4</v>
+      </c>
+      <c r="D135" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136">
-        <v>1200001984</v>
+        <v>1200001985</v>
       </c>
       <c r="B136">
-        <v>40108593</v>
+        <v>40092554</v>
       </c>
       <c r="C136" t="s">
-        <v>141</v>
+        <v>4</v>
       </c>
       <c r="D136" t="s">
-        <v>2</v>
+        <v>146</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137">
-        <v>1200001985</v>
+        <v>1200001987</v>
       </c>
       <c r="B137">
-        <v>40092554</v>
+        <v>40108592</v>
       </c>
       <c r="C137" t="s">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="D137" t="s">
-        <v>2</v>
+        <v>147</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138">
-        <v>1200001987</v>
+        <v>1200002000</v>
       </c>
       <c r="B138">
-        <v>40108592</v>
+        <v>40108590</v>
       </c>
       <c r="C138" t="s">
-        <v>143</v>
+        <v>4</v>
       </c>
       <c r="D138" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139">
-        <v>1200002000</v>
+        <v>1200002002</v>
       </c>
       <c r="B139">
-        <v>40108590</v>
+        <v>40108588</v>
       </c>
       <c r="C139" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D139" t="s">
-        <v>2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140">
-        <v>1200002002</v>
+        <v>1200002007</v>
       </c>
       <c r="B140">
-        <v>40108588</v>
-      </c>
-      <c r="C140" t="s">
-        <v>145</v>
+        <v>40092194</v>
       </c>
       <c r="D140" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141">
-        <v>1200002007</v>
+        <v>1200002008</v>
       </c>
       <c r="B141">
-        <v>40092194</v>
-      </c>
-      <c r="C141" t="s">
-        <v>147</v>
+        <v>40092195</v>
+      </c>
+      <c r="D141" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142">
-        <v>1200002008</v>
+        <v>1200002015</v>
       </c>
       <c r="B142">
-        <v>40092195</v>
+        <v>40108586</v>
       </c>
       <c r="C142" t="s">
-        <v>148</v>
+        <v>4</v>
+      </c>
+      <c r="D142" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143">
-        <v>1200002015</v>
+        <v>1200002016</v>
       </c>
       <c r="B143">
-        <v>40108586</v>
+        <v>40108585</v>
       </c>
       <c r="C143" t="s">
-        <v>149</v>
+        <v>4</v>
       </c>
       <c r="D143" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144">
-        <v>1200002016</v>
+        <v>1200002021</v>
       </c>
       <c r="B144">
-        <v>40108585</v>
-      </c>
-      <c r="C144" t="s">
-        <v>150</v>
+        <v>40108583</v>
       </c>
       <c r="D144" t="s">
-        <v>2</v>
+        <v>155</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145">
-        <v>1200002021</v>
+        <v>1200002024</v>
       </c>
       <c r="B145">
-        <v>40108583</v>
-      </c>
-      <c r="C145" t="s">
-        <v>151</v>
+        <v>40108582</v>
+      </c>
+      <c r="D145" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146">
-        <v>1200002024</v>
+        <v>1200002026</v>
       </c>
       <c r="B146">
-        <v>40108582</v>
+        <v>40098814</v>
       </c>
       <c r="C146" t="s">
-        <v>152</v>
+        <v>4</v>
+      </c>
+      <c r="D146" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147">
-        <v>1200002026</v>
+        <v>1200002027</v>
       </c>
       <c r="B147">
-        <v>40098814</v>
-      </c>
-      <c r="C147" t="s">
-        <v>153</v>
+        <v>40092315</v>
       </c>
       <c r="D147" t="s">
-        <v>2</v>
+        <v>158</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148">
-        <v>1200002027</v>
+        <v>1200002029</v>
       </c>
       <c r="B148">
-        <v>40092315</v>
-      </c>
-      <c r="C148" t="s">
-        <v>154</v>
+        <v>40108581</v>
+      </c>
+      <c r="D148" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149">
-        <v>1200002029</v>
+        <v>1200002030</v>
       </c>
       <c r="B149">
-        <v>40108581</v>
+        <v>40101694</v>
       </c>
       <c r="C149" t="s">
-        <v>155</v>
+        <v>4</v>
+      </c>
+      <c r="D149" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150">
-        <v>1200002030</v>
+        <v>1200002044</v>
       </c>
       <c r="B150">
-        <v>40101694</v>
+        <v>40102662</v>
       </c>
       <c r="C150" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D150" t="s">
-        <v>2</v>
+        <v>162</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151">
-        <v>1200002044</v>
+        <v>1200002072</v>
       </c>
       <c r="B151">
-        <v>40102662</v>
+        <v>40108579</v>
       </c>
       <c r="C151" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D151" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152">
-        <v>1200002072</v>
+        <v>1200002074</v>
       </c>
       <c r="B152">
-        <v>40108579</v>
-      </c>
-      <c r="C152" t="s">
-        <v>159</v>
+        <v>40108578</v>
       </c>
       <c r="D152" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153">
-        <v>1200002074</v>
+        <v>1200002076</v>
       </c>
       <c r="B153">
-        <v>40108578</v>
-      </c>
-      <c r="C153" t="s">
-        <v>161</v>
+        <v>40092140</v>
+      </c>
+      <c r="D153" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154">
-        <v>1200002076</v>
+        <v>1200002084</v>
       </c>
       <c r="B154">
-        <v>40092140</v>
-      </c>
-      <c r="C154" t="s">
-        <v>162</v>
+        <v>40101697</v>
+      </c>
+      <c r="D154" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155">
-        <v>1200002084</v>
+        <v>1200002087</v>
       </c>
       <c r="B155">
-        <v>40101697</v>
-      </c>
-      <c r="C155" t="s">
-        <v>163</v>
+        <v>40092145</v>
+      </c>
+      <c r="D155" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156">
-        <v>1200002087</v>
+        <v>1200002090</v>
       </c>
       <c r="B156">
-        <v>40092145</v>
-      </c>
-      <c r="C156" t="s">
-        <v>164</v>
+        <v>40098803</v>
+      </c>
+      <c r="D156" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157">
-        <v>1200002090</v>
+        <v>1200002099</v>
       </c>
       <c r="B157">
-        <v>40098803</v>
+        <v>40100722</v>
       </c>
       <c r="C157" t="s">
-        <v>165</v>
+        <v>4</v>
+      </c>
+      <c r="D157" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158">
-        <v>1200002099</v>
+        <v>1200002104</v>
       </c>
       <c r="B158">
-        <v>40100722</v>
-      </c>
-      <c r="C158" t="s">
-        <v>166</v>
+        <v>40108576</v>
       </c>
       <c r="D158" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159">
-        <v>1200002104</v>
+        <v>1200002108</v>
       </c>
       <c r="B159">
-        <v>40108576</v>
+        <v>40108574</v>
       </c>
       <c r="C159" t="s">
-        <v>167</v>
+        <v>4</v>
+      </c>
+      <c r="D159" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160">
-        <v>1200002108</v>
+        <v>1200002114</v>
       </c>
       <c r="B160">
-        <v>40108574</v>
-      </c>
-      <c r="C160" t="s">
-        <v>168</v>
+        <v>40108573</v>
       </c>
       <c r="D160" t="s">
-        <v>2</v>
+        <v>173</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161">
-        <v>1200002114</v>
+        <v>1200002116</v>
       </c>
       <c r="B161">
-        <v>40108573</v>
+        <v>40108571</v>
       </c>
       <c r="C161" t="s">
-        <v>169</v>
+        <v>4</v>
+      </c>
+      <c r="D161" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162">
-        <v>1200002116</v>
+        <v>1200002125</v>
       </c>
       <c r="B162">
-        <v>40108571</v>
+        <v>40108675</v>
       </c>
       <c r="C162" t="s">
-        <v>170</v>
+        <v>4</v>
       </c>
       <c r="D162" t="s">
-        <v>2</v>
+        <v>175</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163">
-        <v>1200002125</v>
+        <v>1200002145</v>
       </c>
       <c r="B163">
-        <v>40108675</v>
-      </c>
-      <c r="C163" t="s">
-        <v>171</v>
+        <v>40092173</v>
       </c>
       <c r="D163" t="s">
-        <v>2</v>
+        <v>176</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164">
-        <v>1200002145</v>
+        <v>1200002160</v>
       </c>
       <c r="B164">
-        <v>40092173</v>
+        <v>40092405</v>
       </c>
       <c r="C164" t="s">
-        <v>172</v>
+        <v>177</v>
+      </c>
+      <c r="D164" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165">
-        <v>1200002160</v>
+        <v>1200002164</v>
       </c>
       <c r="B165">
-        <v>40092405</v>
+        <v>40108567</v>
       </c>
       <c r="C165" t="s">
-        <v>173</v>
+        <v>24</v>
       </c>
       <c r="D165" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166">
-        <v>1200002164</v>
+        <v>1200002181</v>
       </c>
       <c r="B166">
-        <v>40108567</v>
-      </c>
-      <c r="C166" t="s">
-        <v>175</v>
+        <v>40102667</v>
       </c>
       <c r="D166" t="s">
-        <v>21</v>
+        <v>180</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167">
-        <v>1200002181</v>
+        <v>1200002184</v>
       </c>
       <c r="B167">
-        <v>40102667</v>
+        <v>40108672</v>
       </c>
       <c r="C167" t="s">
-        <v>176</v>
+        <v>4</v>
+      </c>
+      <c r="D167" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168">
-        <v>1200002184</v>
+        <v>1200002186</v>
       </c>
       <c r="B168">
-        <v>40108672</v>
+        <v>40108684</v>
       </c>
       <c r="C168" t="s">
-        <v>177</v>
+        <v>4</v>
       </c>
       <c r="D168" t="s">
-        <v>2</v>
+        <v>182</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169">
-        <v>1200002186</v>
+        <v>1200002187</v>
       </c>
       <c r="B169">
-        <v>40108684</v>
-      </c>
-      <c r="C169" t="s">
-        <v>178</v>
+        <v>40092180</v>
       </c>
       <c r="D169" t="s">
-        <v>2</v>
+        <v>183</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170">
-        <v>1200002187</v>
+        <v>1200002207</v>
       </c>
       <c r="B170">
-        <v>40092180</v>
+        <v>40108565</v>
       </c>
       <c r="C170" t="s">
-        <v>179</v>
+        <v>4</v>
+      </c>
+      <c r="D170" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171">
-        <v>1200002207</v>
+        <v>1200002209</v>
       </c>
       <c r="B171">
-        <v>40108565</v>
-      </c>
-      <c r="C171" t="s">
-        <v>180</v>
+        <v>40092357</v>
       </c>
       <c r="D171" t="s">
-        <v>2</v>
+        <v>185</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172">
-        <v>1200002209</v>
+        <v>1200002214</v>
       </c>
       <c r="B172">
-        <v>40092357</v>
-      </c>
-      <c r="C172" t="s">
-        <v>181</v>
+        <v>40092134</v>
+      </c>
+      <c r="D172" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173">
-        <v>1200002214</v>
+        <v>1200002216</v>
       </c>
       <c r="B173">
-        <v>40092134</v>
+        <v>40108563</v>
       </c>
       <c r="C173" t="s">
-        <v>182</v>
+        <v>4</v>
+      </c>
+      <c r="D173" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174">
-        <v>1200002216</v>
+        <v>1200002226</v>
       </c>
       <c r="B174">
-        <v>40101695</v>
+        <v>40092391</v>
       </c>
       <c r="C174" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D174" t="s">
-        <v>2</v>
+        <v>189</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175">
-        <v>1200002216</v>
+        <v>1200002231</v>
       </c>
       <c r="B175">
-        <v>40108563</v>
-      </c>
-      <c r="C175" t="s">
-        <v>183</v>
+        <v>40092349</v>
       </c>
       <c r="D175" t="s">
-        <v>2</v>
+        <v>190</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176">
-        <v>1200002226</v>
+        <v>1200002256</v>
       </c>
       <c r="B176">
-        <v>40092391</v>
+        <v>40108679</v>
       </c>
       <c r="C176" t="s">
-        <v>184</v>
+        <v>4</v>
       </c>
       <c r="D176" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177">
-        <v>1200002231</v>
+        <v>1200002259</v>
       </c>
       <c r="B177">
-        <v>40092349</v>
-      </c>
-      <c r="C177" t="s">
-        <v>186</v>
+        <v>40092469</v>
+      </c>
+      <c r="D177" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178">
-        <v>1200002256</v>
+        <v>1200002263</v>
       </c>
       <c r="B178">
-        <v>40108679</v>
+        <v>40108671</v>
       </c>
       <c r="C178" t="s">
-        <v>187</v>
+        <v>4</v>
       </c>
       <c r="D178" t="s">
-        <v>2</v>
+        <v>193</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179">
-        <v>1200002259</v>
+        <v>1200002273</v>
       </c>
       <c r="B179">
-        <v>40092469</v>
+        <v>40092664</v>
       </c>
       <c r="C179" t="s">
-        <v>188</v>
+        <v>194</v>
+      </c>
+      <c r="D179" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180">
-        <v>1200002263</v>
+        <v>1200002281</v>
       </c>
       <c r="B180">
-        <v>40108671</v>
+        <v>40092661</v>
       </c>
       <c r="C180" t="s">
-        <v>189</v>
+        <v>4</v>
       </c>
       <c r="D180" t="s">
-        <v>2</v>
+        <v>196</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181">
-        <v>1200002273</v>
+        <v>1200002312</v>
       </c>
       <c r="B181">
-        <v>40092664</v>
+        <v>40106659</v>
       </c>
       <c r="C181" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D181" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182">
-        <v>1200002281</v>
+        <v>1200002316</v>
       </c>
       <c r="B182">
-        <v>40092661</v>
+        <v>40101699</v>
       </c>
       <c r="C182" t="s">
-        <v>192</v>
+        <v>4</v>
       </c>
       <c r="D182" t="s">
-        <v>2</v>
+        <v>199</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183">
-        <v>1200002312</v>
+        <v>1200002328</v>
       </c>
       <c r="B183">
-        <v>40106659</v>
+        <v>40106665</v>
       </c>
       <c r="C183" t="s">
-        <v>193</v>
+        <v>4</v>
       </c>
       <c r="D183" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184">
-        <v>1200002316</v>
+        <v>1200002329</v>
       </c>
       <c r="B184">
-        <v>40101699</v>
+        <v>40100726</v>
       </c>
       <c r="C184" t="s">
-        <v>195</v>
+        <v>4</v>
       </c>
       <c r="D184" t="s">
-        <v>2</v>
+        <v>201</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185">
-        <v>1200002328</v>
+        <v>1200002331</v>
       </c>
       <c r="B185">
-        <v>40106665</v>
+        <v>40100729</v>
       </c>
       <c r="C185" t="s">
-        <v>196</v>
+        <v>4</v>
       </c>
       <c r="D185" t="s">
-        <v>2</v>
+        <v>202</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186">
-        <v>1200002329</v>
+        <v>1200002332</v>
       </c>
       <c r="B186">
-        <v>40100726</v>
+        <v>40100730</v>
       </c>
       <c r="C186" t="s">
-        <v>197</v>
+        <v>112</v>
       </c>
       <c r="D186" t="s">
-        <v>2</v>
+        <v>203</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187">
-        <v>1200002331</v>
+        <v>1200002333</v>
       </c>
       <c r="B187">
-        <v>40100729</v>
+        <v>40101696</v>
       </c>
       <c r="C187" t="s">
-        <v>198</v>
+        <v>4</v>
       </c>
       <c r="D187" t="s">
-        <v>2</v>
+        <v>204</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188">
-        <v>1200002332</v>
+        <v>1200002337</v>
       </c>
       <c r="B188">
-        <v>40100730</v>
+        <v>40102660</v>
       </c>
       <c r="C188" t="s">
-        <v>199</v>
+        <v>4</v>
       </c>
       <c r="D188" t="s">
-        <v>109</v>
+        <v>205</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189">
-        <v>1200002333</v>
+        <v>1200002338</v>
       </c>
       <c r="B189">
-        <v>40101696</v>
+        <v>40102661</v>
       </c>
       <c r="C189" t="s">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="D189" t="s">
-        <v>2</v>
+        <v>206</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190">
-        <v>1200002337</v>
+        <v>1200002339</v>
       </c>
       <c r="B190">
-        <v>40102660</v>
+        <v>40102663</v>
       </c>
       <c r="C190" t="s">
-        <v>201</v>
+        <v>4</v>
       </c>
       <c r="D190" t="s">
-        <v>2</v>
+        <v>207</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191">
-        <v>1200002338</v>
+        <v>1200002341</v>
       </c>
       <c r="B191">
-        <v>40102661</v>
+        <v>40102664</v>
       </c>
       <c r="C191" t="s">
-        <v>202</v>
+        <v>4</v>
       </c>
       <c r="D191" t="s">
-        <v>2</v>
+        <v>208</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192">
-        <v>1200002339</v>
+        <v>1200002342</v>
       </c>
       <c r="B192">
-        <v>40102663</v>
+        <v>40102665</v>
       </c>
       <c r="C192" t="s">
-        <v>203</v>
+        <v>4</v>
       </c>
       <c r="D192" t="s">
-        <v>2</v>
+        <v>209</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193">
-        <v>1200002341</v>
+        <v>1200002348</v>
       </c>
       <c r="B193">
-        <v>40102664</v>
+        <v>40103642</v>
       </c>
       <c r="C193" t="s">
-        <v>204</v>
+        <v>4</v>
       </c>
       <c r="D193" t="s">
-        <v>2</v>
+        <v>210</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194">
-        <v>1200002342</v>
+        <v>1200002352</v>
       </c>
       <c r="B194">
-        <v>40102665</v>
+        <v>40105672</v>
       </c>
       <c r="C194" t="s">
-        <v>205</v>
+        <v>4</v>
       </c>
       <c r="D194" t="s">
-        <v>2</v>
+        <v>211</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195">
-        <v>1200002348</v>
+        <v>1200002356</v>
       </c>
       <c r="B195">
-        <v>40103642</v>
+        <v>40105673</v>
       </c>
       <c r="C195" t="s">
-        <v>206</v>
+        <v>4</v>
       </c>
       <c r="D195" t="s">
-        <v>2</v>
+        <v>212</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196">
-        <v>1200002352</v>
+        <v>1200002361</v>
       </c>
       <c r="B196">
-        <v>40105672</v>
+        <v>40105674</v>
       </c>
       <c r="C196" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="D196" t="s">
-        <v>2</v>
+        <v>213</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197">
-        <v>1200002356</v>
+        <v>1200002362</v>
       </c>
       <c r="B197">
-        <v>40105673</v>
+        <v>40107610</v>
       </c>
       <c r="C197" t="s">
-        <v>207</v>
+        <v>4</v>
       </c>
       <c r="D197" t="s">
-        <v>2</v>
+        <v>214</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198">
-        <v>1200002361</v>
+        <v>1200002366</v>
       </c>
       <c r="B198">
-        <v>40105674</v>
+        <v>40105675</v>
       </c>
       <c r="C198" t="s">
-        <v>208</v>
+        <v>4</v>
       </c>
       <c r="D198" t="s">
-        <v>2</v>
+        <v>215</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199">
-        <v>1200002362</v>
+        <v>1200002368</v>
       </c>
       <c r="B199">
-        <v>40107610</v>
+        <v>40105676</v>
       </c>
       <c r="C199" t="s">
-        <v>209</v>
+        <v>4</v>
       </c>
       <c r="D199" t="s">
-        <v>2</v>
+        <v>216</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200">
-        <v>1200002366</v>
+        <v>1200002369</v>
       </c>
       <c r="B200">
-        <v>40105675</v>
+        <v>40106660</v>
       </c>
       <c r="C200" t="s">
-        <v>210</v>
+        <v>4</v>
       </c>
       <c r="D200" t="s">
-        <v>2</v>
+        <v>217</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201">
-        <v>1200002368</v>
+        <v>1200002370</v>
       </c>
       <c r="B201">
-        <v>40105676</v>
+        <v>40106662</v>
       </c>
       <c r="C201" t="s">
-        <v>211</v>
+        <v>65</v>
       </c>
       <c r="D201" t="s">
-        <v>2</v>
+        <v>218</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202">
-        <v>1200002369</v>
+        <v>1200002381</v>
       </c>
       <c r="B202">
-        <v>40106660</v>
+        <v>40106669</v>
       </c>
       <c r="C202" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D202" t="s">
-        <v>2</v>
+        <v>220</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203">
-        <v>1200002370</v>
+        <v>1200002382</v>
       </c>
       <c r="B203">
-        <v>40106661</v>
+        <v>40106672</v>
       </c>
       <c r="C203" t="s">
-        <v>213</v>
+        <v>4</v>
       </c>
       <c r="D203" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204">
-        <v>1200002370</v>
+        <v>1200002385</v>
       </c>
       <c r="B204">
-        <v>40106662</v>
+        <v>40107608</v>
       </c>
       <c r="C204" t="s">
-        <v>213</v>
+        <v>4</v>
       </c>
       <c r="D204" t="s">
-        <v>62</v>
+        <v>222</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205">
-        <v>1200002381</v>
+        <v>1200002386</v>
       </c>
       <c r="B205">
-        <v>40106669</v>
+        <v>40107612</v>
       </c>
       <c r="C205" t="s">
-        <v>214</v>
+        <v>4</v>
       </c>
       <c r="D205" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206">
-        <v>1200002382</v>
+        <v>1200002387</v>
       </c>
       <c r="B206">
-        <v>40106672</v>
+        <v>40107613</v>
       </c>
       <c r="C206" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="D206" t="s">
-        <v>2</v>
+        <v>224</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207">
-        <v>1200002385</v>
+        <v>1200002388</v>
       </c>
       <c r="B207">
-        <v>40107608</v>
+        <v>40108555</v>
       </c>
       <c r="C207" t="s">
-        <v>217</v>
+        <v>4</v>
       </c>
       <c r="D207" t="s">
-        <v>2</v>
+        <v>225</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208">
-        <v>1200002386</v>
+        <v>1200002389</v>
       </c>
       <c r="B208">
-        <v>40107612</v>
+        <v>40108681</v>
       </c>
       <c r="C208" t="s">
-        <v>218</v>
+        <v>24</v>
       </c>
       <c r="D208" t="s">
-        <v>2</v>
+        <v>226</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209">
-        <v>1200002387</v>
+        <v>1200002390</v>
       </c>
       <c r="B209">
-        <v>40107613</v>
+        <v>40108682</v>
       </c>
       <c r="C209" t="s">
-        <v>219</v>
+        <v>4</v>
       </c>
       <c r="D209" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210">
-        <v>1200002388</v>
+        <v>1200002391</v>
       </c>
       <c r="B210">
-        <v>40108555</v>
+        <v>40108556</v>
       </c>
       <c r="C210" t="s">
-        <v>220</v>
+        <v>4</v>
       </c>
       <c r="D210" t="s">
-        <v>2</v>
+        <v>228</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211">
-        <v>1200002389</v>
+        <v>1200002397</v>
       </c>
       <c r="B211">
-        <v>40108681</v>
-      </c>
-      <c r="C211" t="s">
-        <v>221</v>
+        <v>40108680</v>
       </c>
       <c r="D211" t="s">
-        <v>21</v>
+        <v>229</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212">
-        <v>1200002390</v>
+        <v>1200002398</v>
       </c>
       <c r="B212">
-        <v>40108682</v>
+        <v>40108557</v>
       </c>
       <c r="C212" t="s">
-        <v>222</v>
+        <v>4</v>
       </c>
       <c r="D212" t="s">
-        <v>2</v>
+        <v>230</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213">
-        <v>1200002391</v>
+        <v>1200002399</v>
       </c>
       <c r="B213">
-        <v>40108556</v>
+        <v>40108678</v>
       </c>
       <c r="C213" t="s">
-        <v>223</v>
+        <v>24</v>
       </c>
       <c r="D213" t="s">
-        <v>2</v>
+        <v>231</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214">
-        <v>1200002397</v>
+        <v>1200002400</v>
       </c>
       <c r="B214">
-        <v>40108680</v>
+        <v>40108683</v>
       </c>
       <c r="C214" t="s">
-        <v>224</v>
+        <v>4</v>
+      </c>
+      <c r="D214" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215">
-        <v>1200002398</v>
+        <v>1200002401</v>
       </c>
       <c r="B215">
-        <v>40108557</v>
+        <v>40108685</v>
       </c>
       <c r="C215" t="s">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="D215" t="s">
-        <v>2</v>
+        <v>233</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216">
-        <v>1200002399</v>
+        <v>1200002402</v>
       </c>
       <c r="B216">
-        <v>40108678</v>
+        <v>40108687</v>
       </c>
       <c r="C216" t="s">
-        <v>226</v>
+        <v>4</v>
       </c>
       <c r="D216" t="s">
-        <v>21</v>
+        <v>234</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217">
-        <v>1200002400</v>
+        <v>1200002425</v>
       </c>
       <c r="B217">
-        <v>40108683</v>
+        <v>40110591</v>
       </c>
       <c r="C217" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="D217" t="s">
-        <v>2</v>
+        <v>236</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218">
-        <v>1200002401</v>
+        <v>1200002289</v>
       </c>
       <c r="B218">
-        <v>40108685</v>
+        <v>40092677</v>
       </c>
       <c r="C218" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D218" t="s">
-        <v>158</v>
+        <v>238</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219">
-        <v>1200002402</v>
+        <v>1200001978</v>
       </c>
       <c r="B219">
-        <v>40108687</v>
+        <v>40109627</v>
       </c>
       <c r="C219" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D219" t="s">
-        <v>2</v>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <v>1200001289</v>
+      </c>
+      <c r="B220" t="s">
+        <v>5</v>
+      </c>
+      <c r="C220" t="s">
+        <v>241</v>
+      </c>
+      <c r="D220" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <v>1200001920</v>
+      </c>
+      <c r="B221">
+        <v>40109627</v>
+      </c>
+      <c r="C221" t="s">
+        <v>243</v>
+      </c>
+      <c r="D221" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <v>1200002056</v>
+      </c>
+      <c r="B222">
+        <v>40092303</v>
+      </c>
+      <c r="C222" t="s">
+        <v>245</v>
+      </c>
+      <c r="D222" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <v>1200002057</v>
+      </c>
+      <c r="B223">
+        <v>336512</v>
+      </c>
+      <c r="C223" t="s">
+        <v>247</v>
+      </c>
+      <c r="D223" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <v>1200002111</v>
+      </c>
+      <c r="B224">
+        <v>40092276</v>
+      </c>
+      <c r="C224" t="s">
+        <v>249</v>
+      </c>
+      <c r="D224" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <v>1200002136</v>
+      </c>
+      <c r="B225">
+        <v>40092128</v>
+      </c>
+      <c r="C225" t="s">
+        <v>251</v>
+      </c>
+      <c r="D225" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <v>1200002232</v>
+      </c>
+      <c r="B226">
+        <v>40092245</v>
+      </c>
+      <c r="C226" t="s">
+        <v>253</v>
+      </c>
+      <c r="D226" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A227">
+        <v>1200002264</v>
+      </c>
+      <c r="B227">
+        <v>40094366</v>
+      </c>
+      <c r="C227" t="s">
+        <v>255</v>
+      </c>
+      <c r="D227" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A228">
+        <v>1200002272</v>
+      </c>
+      <c r="B228">
+        <v>40092680</v>
+      </c>
+      <c r="C228" t="s">
+        <v>257</v>
+      </c>
+      <c r="D228" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A229">
+        <v>1200002282</v>
+      </c>
+      <c r="B229">
+        <v>40092665</v>
+      </c>
+      <c r="C229" t="s">
+        <v>5</v>
+      </c>
+      <c r="D229" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A230">
+        <v>1200002284</v>
+      </c>
+      <c r="B230">
+        <v>40092668</v>
+      </c>
+      <c r="C230" t="s">
+        <v>5</v>
+      </c>
+      <c r="D230" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A231">
+        <v>1200002290</v>
+      </c>
+      <c r="B231">
+        <v>40110584</v>
+      </c>
+      <c r="C231" t="s">
+        <v>261</v>
+      </c>
+      <c r="D231" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A232">
+        <v>1200002291</v>
+      </c>
+      <c r="B232" t="s">
+        <v>5</v>
+      </c>
+      <c r="C232" t="s">
+        <v>263</v>
+      </c>
+      <c r="D232" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A233">
+        <v>1200002301</v>
+      </c>
+      <c r="B233">
+        <v>40096118</v>
+      </c>
+      <c r="C233" t="s">
+        <v>265</v>
+      </c>
+      <c r="D233" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A234">
+        <v>1200002384</v>
+      </c>
+      <c r="B234">
+        <v>40106671</v>
+      </c>
+      <c r="C234" t="s">
+        <v>267</v>
+      </c>
+      <c r="D234" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A235">
+        <v>1200002404</v>
+      </c>
+      <c r="B235">
+        <v>40109621</v>
+      </c>
+      <c r="C235" t="s">
+        <v>269</v>
+      </c>
+      <c r="D235" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A236">
+        <v>1200002406</v>
+      </c>
+      <c r="B236">
+        <v>40109622</v>
+      </c>
+      <c r="C236" t="s">
+        <v>271</v>
+      </c>
+      <c r="D236" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A237">
+        <v>1200002407</v>
+      </c>
+      <c r="B237">
+        <v>40109620</v>
+      </c>
+      <c r="C237" t="s">
+        <v>273</v>
+      </c>
+      <c r="D237" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A238">
+        <v>1200002418</v>
+      </c>
+      <c r="B238">
+        <v>40109625</v>
+      </c>
+      <c r="C238" t="s">
+        <v>275</v>
+      </c>
+      <c r="D238" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A239">
+        <v>1200002419</v>
+      </c>
+      <c r="B239">
+        <v>40109626</v>
+      </c>
+      <c r="C239" t="s">
+        <v>277</v>
+      </c>
+      <c r="D239" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A240">
+        <v>1200002420</v>
+      </c>
+      <c r="B240">
+        <v>40109632</v>
+      </c>
+      <c r="C240" t="s">
+        <v>279</v>
+      </c>
+      <c r="D240" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A241">
+        <v>1200002421</v>
+      </c>
+      <c r="B241">
+        <v>40109631</v>
+      </c>
+      <c r="C241" t="s">
+        <v>281</v>
+      </c>
+      <c r="D241" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A242">
+        <v>1200002422</v>
+      </c>
+      <c r="B242">
+        <v>40109630</v>
+      </c>
+      <c r="C242" t="s">
+        <v>283</v>
+      </c>
+      <c r="D242" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A243">
+        <v>1200002423</v>
+      </c>
+      <c r="B243">
+        <v>40109629</v>
+      </c>
+      <c r="C243" t="s">
+        <v>285</v>
+      </c>
+      <c r="D243" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A244">
+        <v>1200002424</v>
+      </c>
+      <c r="B244">
+        <v>40110590</v>
+      </c>
+      <c r="C244" t="s">
+        <v>287</v>
+      </c>
+      <c r="D244" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>
